--- a/data/trans_orig/P15E_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P15E_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población mayor de 65 años según si ha sufrido alguna caída que precise atención sanitaria en el último año en 2023</t>
+          <t>Población mayor de 65 años según si ha sufrido alguna caída que precise atención sanitaria en el último año en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1053</t>
+          <t>889</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4265</t>
+          <t>4058</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>71,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>1468</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5373</t>
+          <t>5266</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>66,17%</t>
+          <t>64,86%</t>
         </is>
       </c>
     </row>
@@ -843,97 +843,97 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>30,57%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="R5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>769</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>13,49%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>811</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1435</t>
+          <t>1642</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4647</t>
+          <t>4811</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>84,41%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2746</t>
+          <t>2853</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6869</t>
+          <t>6651</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>81,91%</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3624</t>
+          <t>3647</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,75%</t>
+          <t>70,19%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>451</t>
+          <t>442</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3146</t>
+          <t>3137</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1553</t>
+          <t>1467</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5960</t>
+          <t>5892</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,93%</t>
+          <t>66,16%</t>
         </is>
       </c>
     </row>
@@ -1299,97 +1299,97 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>1078</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>20,75%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="R9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>862</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>23,25%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>1054</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1571</t>
+          <t>1552</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>566</t>
+          <t>572</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3258</t>
+          <t>3267</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>88,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2945</t>
+          <t>3013</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7352</t>
+          <t>7438</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>83,53%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>404</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3390</t>
+          <t>3363</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>981</t>
+          <t>1136</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4373</t>
+          <t>4574</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>72,79%</t>
+          <t>76,15%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2401</t>
+          <t>2289</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6813</t>
+          <t>6833</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>70,09%</t>
+          <t>70,3%</t>
         </is>
       </c>
     </row>
@@ -1755,97 +1755,97 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>998</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>863</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>2729</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>16,62%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>23,25%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>45,44%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>998</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>2820</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>16,62%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>3001</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>10,27%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>46,94%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>998</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>3193</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>10,27%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>30,87%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>347</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3159</t>
+          <t>3301</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>88,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>880</t>
+          <t>871</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4298</t>
+          <t>4059</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>67,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t>2035</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6493</t>
+          <t>6787</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,8%</t>
+          <t>69,83%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2841</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8866</t>
+          <t>8834</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>58,12%</t>
+          <t>57,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1160</t>
+          <t>1124</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5047</t>
+          <t>5346</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,35%</t>
+          <t>46,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4955</t>
+          <t>5316</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12499</t>
+          <t>12699</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>46,94%</t>
+          <t>47,69%</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>336</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4375</t>
+          <t>4292</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2226,12 +2226,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3300</t>
+          <t>3101</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>826</t>
+          <t>769</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5889</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>20,17%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10738</t>
+          <t>11060</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>70,4%</t>
+          <t>72,51%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5159</t>
+          <t>5307</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9595</t>
+          <t>9582</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>46,64%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>11722</t>
+          <t>11174</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>19394</t>
+          <t>18932</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>44,02%</t>
+          <t>41,96%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>71,09%</t>
         </is>
       </c>
     </row>
@@ -2554,12 +2554,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>482</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4023</t>
+          <t>3848</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>60,43%</t>
+          <t>57,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2471</t>
+          <t>2459</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7655</t>
+          <t>7511</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3786</t>
+          <t>3753</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>9972</t>
+          <t>10179</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,12 +2639,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>32,66%</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2572</t>
+          <t>2747</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2415</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7784</t>
+          <t>8064</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2671</t>
+          <t>2711</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>8732</t>
+          <t>9033</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2752,12 +2752,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>28,98%</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2054</t>
+          <t>2221</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5738</t>
+          <t>5735</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11987</t>
+          <t>11981</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18318</t>
+          <t>18337</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2830,12 +2830,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>48,9%</t>
+          <t>48,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>74,73%</t>
+          <t>74,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2850,12 +2850,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>15802</t>
+          <t>15473</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>23162</t>
+          <t>22827</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>50,69%</t>
+          <t>49,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>74,31%</t>
+          <t>73,23%</t>
         </is>
       </c>
     </row>
@@ -3045,12 +3045,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5050</t>
+          <t>5026</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>12401</t>
+          <t>11931</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>40,2%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3080,12 +3080,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>5050</t>
+          <t>5026</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>12401</t>
+          <t>11931</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3095,12 +3095,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>40,2%</t>
         </is>
       </c>
     </row>
@@ -3158,12 +3158,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>504</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4503</t>
+          <t>4330</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3173,12 +3173,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3193,12 +3193,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>504</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4503</t>
+          <t>4330</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>14,59%</t>
         </is>
       </c>
     </row>
@@ -3271,12 +3271,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>15544</t>
+          <t>15558</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>23148</t>
+          <t>22954</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3286,12 +3286,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>52,42%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>77,99%</t>
+          <t>77,34%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3306,12 +3306,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>15544</t>
+          <t>15558</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>23148</t>
+          <t>22954</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>52,42%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>77,99%</t>
+          <t>77,34%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>7615</t>
+          <t>7753</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>16351</t>
+          <t>16519</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>49,19%</t>
+          <t>49,7%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>17167</t>
+          <t>16415</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>28658</t>
+          <t>27934</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>27003</t>
+          <t>27186</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>41309</t>
+          <t>41700</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>36,51%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>603</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>5114</t>
+          <t>5208</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>5235</t>
+          <t>4925</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>12936</t>
+          <t>13303</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6909</t>
+          <t>6775</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>15488</t>
+          <t>15782</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,82%</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>14232</t>
+          <t>14193</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>23475</t>
+          <t>23238</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>42,7%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>70,63%</t>
+          <t>69,92%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>43796</t>
+          <t>43902</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>55780</t>
+          <t>55990</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>54,08%</t>
+          <t>54,21%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>68,88%</t>
+          <t>69,14%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>61621</t>
+          <t>62313</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>76599</t>
+          <t>77337</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>54,55%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>67,06%</t>
+          <t>67,71%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P15E_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P15E_2023-Clase-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>614</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -735,12 +735,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2276</t>
+          <t>2553</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>81,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2491</t>
+          <t>2687</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>889</t>
+          <t>1084</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4058</t>
+          <t>4844</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>37,83%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>71,19%</t>
+          <t>68,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>3137</t>
+          <t>3301</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1468</t>
+          <t>1454</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5266</t>
+          <t>6035</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>64,86%</t>
+          <t>58,92%</t>
         </is>
       </c>
     </row>
@@ -951,27 +951,27 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1772</t>
+          <t>2528</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>143</t>
+          <t>589</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2419</t>
+          <t>3142</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>73,26%</t>
+          <t>80,45%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3209</t>
+          <t>4415</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1642</t>
+          <t>2258</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4811</t>
+          <t>6018</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>56,31%</t>
+          <t>62,17%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>84,41%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>4982</t>
+          <t>6943</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2853</t>
+          <t>4209</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6651</t>
+          <t>8790</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>61,36%</t>
+          <t>67,78%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>81,91%</t>
+          <t>85,81%</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2419</t>
+          <t>3142</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2419</t>
+          <t>3142</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2419</t>
+          <t>3142</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5700</t>
+          <t>7102</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5700</t>
+          <t>7102</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5700</t>
+          <t>7102</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>8119</t>
+          <t>10244</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8119</t>
+          <t>10244</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8119</t>
+          <t>10244</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1566</t>
+          <t>1727</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1191,12 +1191,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3647</t>
+          <t>4113</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>70,19%</t>
+          <t>71,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1966</t>
+          <t>2134</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>574</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3137</t>
+          <t>3415</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>53,01%</t>
+          <t>53,7%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>3860</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1467</t>
+          <t>1454</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5892</t>
+          <t>6435</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>39,55%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,16%</t>
+          <t>65,94%</t>
         </is>
       </c>
     </row>
@@ -1407,27 +1407,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3630</t>
+          <t>4060</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1552</t>
+          <t>1666</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5196</t>
+          <t>5787</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>69,85%</t>
+          <t>70,16%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1743</t>
+          <t>1839</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>557</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3267</t>
+          <t>3397</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>46,99%</t>
+          <t>46,3%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>5372</t>
+          <t>5899</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3013</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7438</t>
+          <t>8305</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>60,33%</t>
+          <t>60,45%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>85,1%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5196</t>
+          <t>5787</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5196</t>
+          <t>5787</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5196</t>
+          <t>5787</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3709</t>
+          <t>3973</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3709</t>
+          <t>3973</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3709</t>
+          <t>3973</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>8905</t>
+          <t>9759</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>8905</t>
+          <t>9759</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8905</t>
+          <t>9759</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1637,32 +1637,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1953</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>739</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3363</t>
+          <t>4030</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>52,6%</t>
+          <t>60,21%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1672,32 +1672,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>2868</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1136</t>
+          <t>1230</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4574</t>
+          <t>4900</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>43,53%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>76,15%</t>
+          <t>74,37%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>4592</t>
+          <t>5513</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2289</t>
+          <t>3141</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6833</t>
+          <t>7999</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>50,2%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>70,3%</t>
+          <t>72,83%</t>
         </is>
       </c>
     </row>
@@ -1785,7 +1785,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>998</t>
+          <t>1054</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2729</t>
+          <t>3199</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>48,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>998</t>
+          <t>1054</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3001</t>
+          <t>3452</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>31,43%</t>
         </is>
       </c>
     </row>
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1760</t>
+          <t>1748</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>347</t>
+          <t>363</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3301</t>
+          <t>3654</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>47,4%</t>
+          <t>39,79%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>83,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2370</t>
+          <t>2667</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>871</t>
+          <t>954</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4059</t>
+          <t>4590</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>67,57%</t>
+          <t>69,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>4130</t>
+          <t>4415</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2035</t>
+          <t>1972</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6787</t>
+          <t>6954</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>40,2%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,83%</t>
+          <t>63,32%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3713</t>
+          <t>4393</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3713</t>
+          <t>4393</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3713</t>
+          <t>4393</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6007</t>
+          <t>6589</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6007</t>
+          <t>6589</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6007</t>
+          <t>6589</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>9720</t>
+          <t>10982</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>9720</t>
+          <t>10982</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>9720</t>
+          <t>10982</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2093,32 +2093,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>5789</t>
+          <t>6105</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2841</t>
+          <t>3181</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8834</t>
+          <t>9809</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>57,92%</t>
+          <t>59,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,32 +2128,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2767</t>
+          <t>2857</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1124</t>
+          <t>1061</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5346</t>
+          <t>5253</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>46,98%</t>
+          <t>43,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>8555</t>
+          <t>8962</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5316</t>
+          <t>5163</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12699</t>
+          <t>13020</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>45,45%</t>
         </is>
       </c>
     </row>
@@ -2206,32 +2206,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1552</t>
+          <t>1460</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>344</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4292</t>
+          <t>4247</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>993</t>
+          <t>1092</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3101</t>
+          <t>3403</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>2544</t>
+          <t>2552</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>769</t>
+          <t>838</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>5835</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,37%</t>
         </is>
       </c>
     </row>
@@ -2319,32 +2319,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7913</t>
+          <t>8963</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>5510</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11060</t>
+          <t>12181</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>51,88%</t>
+          <t>54,23%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>33,34%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>72,51%</t>
+          <t>73,7%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>7619</t>
+          <t>8169</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5307</t>
+          <t>5824</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9582</t>
+          <t>10273</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>66,96%</t>
+          <t>67,41%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>46,64%</t>
+          <t>48,06%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>84,78%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>15532</t>
+          <t>17132</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>11174</t>
+          <t>12586</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>18932</t>
+          <t>21096</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>58,32%</t>
+          <t>59,81%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>41,96%</t>
+          <t>43,94%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>71,09%</t>
+          <t>73,64%</t>
         </is>
       </c>
     </row>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>15253</t>
+          <t>16528</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15253</t>
+          <t>16528</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15253</t>
+          <t>16528</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>11379</t>
+          <t>12118</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11379</t>
+          <t>12118</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11379</t>
+          <t>12118</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>26631</t>
+          <t>28646</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>26631</t>
+          <t>28646</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>26631</t>
+          <t>28646</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2549,32 +2549,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1940</t>
+          <t>1960</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>499</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3848</t>
+          <t>3854</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>57,8%</t>
+          <t>56,7%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,32 +2584,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>4563</t>
+          <t>4722</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2459</t>
+          <t>2480</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7511</t>
+          <t>7553</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>6503</t>
+          <t>6682</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3753</t>
+          <t>4025</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10179</t>
+          <t>10584</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>32,45%</t>
         </is>
       </c>
     </row>
@@ -2662,7 +2662,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>650</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2672,12 +2672,12 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2747</t>
+          <t>3137</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>46,15%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,32 +2697,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4607</t>
+          <t>4963</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2415</t>
+          <t>2685</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8064</t>
+          <t>8694</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>33,67%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,32 +2732,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>5613</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2711</t>
+          <t>2977</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>9033</t>
+          <t>9112</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>27,93%</t>
         </is>
       </c>
     </row>
@@ -2775,32 +2775,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>4075</t>
+          <t>4187</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2221</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5735</t>
+          <t>5851</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>61,21%</t>
+          <t>61,6%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>35,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2810,32 +2810,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>15344</t>
+          <t>16137</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11981</t>
+          <t>12491</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18337</t>
+          <t>19289</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>62,49%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>48,37%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>74,8%</t>
+          <t>74,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,32 +2845,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>19418</t>
+          <t>20324</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>15473</t>
+          <t>16354</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>22827</t>
+          <t>24144</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>62,3%</t>
+          <t>62,31%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>49,64%</t>
+          <t>50,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>73,23%</t>
+          <t>74,02%</t>
         </is>
       </c>
     </row>
@@ -2888,17 +2888,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>6657</t>
+          <t>6798</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>6657</t>
+          <t>6798</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6657</t>
+          <t>6798</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2923,17 +2923,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>24514</t>
+          <t>25822</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>24514</t>
+          <t>25822</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>24514</t>
+          <t>25822</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>31171</t>
+          <t>32619</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>31171</t>
+          <t>32619</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>31171</t>
+          <t>32619</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2990,7 +2990,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -3040,32 +3040,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>8059</t>
+          <t>8167</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5026</t>
+          <t>4952</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>11931</t>
+          <t>11986</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,32 +3075,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>8059</t>
+          <t>8167</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>5026</t>
+          <t>4952</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>11931</t>
+          <t>11986</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>38,15%</t>
         </is>
       </c>
     </row>
@@ -3153,32 +3153,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1866</t>
+          <t>1888</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>504</t>
+          <t>601</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4330</t>
+          <t>5052</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,32 +3188,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1866</t>
+          <t>1888</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>504</t>
+          <t>601</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4330</t>
+          <t>5052</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>16,08%</t>
         </is>
       </c>
     </row>
@@ -3266,32 +3266,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>19754</t>
+          <t>21362</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>15558</t>
+          <t>17086</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>22954</t>
+          <t>24949</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>66,56%</t>
+          <t>67,99%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>52,42%</t>
+          <t>54,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>77,34%</t>
+          <t>79,41%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,32 +3301,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>19754</t>
+          <t>21362</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>15558</t>
+          <t>17086</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>22954</t>
+          <t>24949</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>66,56%</t>
+          <t>67,99%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>52,42%</t>
+          <t>54,38%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>77,34%</t>
+          <t>79,41%</t>
         </is>
       </c>
     </row>
@@ -3379,17 +3379,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>29679</t>
+          <t>31417</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>29679</t>
+          <t>31417</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>29679</t>
+          <t>31417</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3414,17 +3414,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>29679</t>
+          <t>31417</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>29679</t>
+          <t>31417</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>29679</t>
+          <t>31417</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3461,22 +3461,22 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>11895</t>
+          <t>13052</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>7753</t>
+          <t>8546</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>16519</t>
+          <t>17874</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>48,77%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,32 +3496,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>22484</t>
+          <t>23434</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>16415</t>
+          <t>17501</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>27934</t>
+          <t>29772</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,32 +3531,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>34379</t>
+          <t>36486</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>27186</t>
+          <t>29097</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>41700</t>
+          <t>44932</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>36,33%</t>
         </is>
       </c>
     </row>
@@ -3574,32 +3574,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2194</t>
+          <t>2110</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>614</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>5208</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,32 +3609,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>8465</t>
+          <t>8997</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>4925</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>13303</t>
+          <t>13627</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,32 +3644,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>10658</t>
+          <t>11107</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6775</t>
+          <t>7077</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>15782</t>
+          <t>16952</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,71%</t>
         </is>
       </c>
     </row>
@@ -3687,32 +3687,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>19149</t>
+          <t>21486</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>14193</t>
+          <t>16514</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>23238</t>
+          <t>26354</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>57,61%</t>
+          <t>58,63%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>45,06%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>71,91%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,32 +3722,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>50039</t>
+          <t>54590</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>43902</t>
+          <t>47664</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>55990</t>
+          <t>61309</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>61,79%</t>
+          <t>62,73%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>54,21%</t>
+          <t>54,77%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>69,14%</t>
+          <t>70,45%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,32 +3757,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>69188</t>
+          <t>76076</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>62313</t>
+          <t>67311</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>77337</t>
+          <t>84017</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>60,57%</t>
+          <t>61,52%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>54,55%</t>
+          <t>54,43%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>67,71%</t>
+          <t>67,94%</t>
         </is>
       </c>
     </row>
@@ -3800,17 +3800,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>33238</t>
+          <t>36648</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>33238</t>
+          <t>36648</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>33238</t>
+          <t>36648</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3835,17 +3835,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>80987</t>
+          <t>87020</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>80987</t>
+          <t>87020</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>80987</t>
+          <t>87020</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3870,17 +3870,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>114225</t>
+          <t>123668</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>114225</t>
+          <t>123668</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>114225</t>
+          <t>123668</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
